--- a/jogos_2024-12-04.xlsx
+++ b/jogos_2024-12-04.xlsx
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3.48</v>
+        <v>5.2</v>
       </c>
       <c r="N14" t="n">
-        <v>4.64</v>
+        <v>7.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="R14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['1', '17', '20', '30', '88']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AI14" t="n">
         <v>1.4</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45630.5625</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['69', '90']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['38', '78']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.36</v>
       </c>
-      <c r="M15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['1', '17', '20', '30', '88']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AI15" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.2</v>
+        <v>1.72</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45630.5625</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.08</v>
+        <v>1.78</v>
       </c>
       <c r="M16" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="N16" t="n">
-        <v>2.36</v>
+        <v>4.64</v>
       </c>
       <c r="O16" t="n">
-        <v>4.04</v>
+        <v>2.63</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
         <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['51', '56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45630.5625</v>
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="M17" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>4.04</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="Y17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.92</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['69', '90']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['38', '78']</t>
+          <t>['51', '56']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45630.5625</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,109 +2836,109 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>GOŠK Gabela</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.23</v>
+        <v>14.59</v>
       </c>
       <c r="M19" t="n">
-        <v>6.29</v>
+        <v>7.14</v>
       </c>
       <c r="N19" t="n">
-        <v>10.7</v>
+        <v>1.11</v>
       </c>
       <c r="O19" t="n">
-        <v>1.62</v>
+        <v>11</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>1.53</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['14', '80']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AI19" t="n">
         <v>6</v>
       </c>
-      <c r="Y19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['17', '38', '62']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['80']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45630.60416666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GOŠK Gabela</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>14.59</v>
+        <v>1.23</v>
       </c>
       <c r="M20" t="n">
-        <v>7.14</v>
+        <v>6.29</v>
       </c>
       <c r="N20" t="n">
-        <v>1.11</v>
+        <v>10.7</v>
       </c>
       <c r="O20" t="n">
-        <v>11</v>
+        <v>1.62</v>
       </c>
       <c r="P20" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.53</v>
+        <v>8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="V20" t="n">
         <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.32</v>
+        <v>2.99</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '38', '62']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['14', '80']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>1.18</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45630.60416666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.45</v>
+        <v>6.27</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>1.66</v>
       </c>
       <c r="N22" t="n">
-        <v>5.75</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
-        <v>2.05</v>
+        <v>4.33</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
         <v>1.36</v>
@@ -3279,53 +3279,53 @@
         <v>1.44</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2</v>
       </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['7', '8', '13', '17', '42']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '64']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45630.625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,22 +3378,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.27</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
-        <v>1.66</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.88</v>
+        <v>5.75</v>
       </c>
       <c r="O23" t="n">
-        <v>4.33</v>
+        <v>2.05</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="R23" t="n">
         <v>1.36</v>
@@ -3408,53 +3408,53 @@
         <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
+          <t>['7', '8', '13', '17', '42']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['11', '64']</t>
-        </is>
-      </c>
       <c r="AG23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.53</v>
+        <v>3.5</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45630.625</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
         <v>3</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,22 +3636,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
         <v>1.44</v>
@@ -3666,53 +3666,53 @@
         <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '20', '34']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['12', '16', '51']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45630.66666666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,109 +3739,109 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="M26" t="n">
-        <v>1.73</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>8.460000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="O26" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.3</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.16</v>
-      </c>
       <c r="X26" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['25', '29']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['16', '80']</t>
+          <t>['12', '16', '51']</t>
         </is>
       </c>
       <c r="AG26" t="n">
         <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45630.66666666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,109 +3868,109 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="I27" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.62</v>
+        <v>2.41</v>
       </c>
       <c r="M27" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="N27" t="n">
-        <v>4.5</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>2.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="X27" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.55</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['17', '20', '34']</t>
+          <t>['25', '29']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['16', '80']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="AI27" t="n">
         <v>1.44</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45630.66666666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,65 +4023,65 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="M28" t="n">
-        <v>7.22</v>
+        <v>6.34</v>
       </c>
       <c r="N28" t="n">
-        <v>7.85</v>
+        <v>6.89</v>
       </c>
       <c r="O28" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['10', '33', '49', '72']</t>
+          <t>['34', '36', '50', '75']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.81</v>
+        <v>3.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45630.6875</v>
@@ -4126,109 +4126,109 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
         <v>3</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.07</v>
+        <v>2.1</v>
       </c>
       <c r="M29" t="n">
-        <v>13.3</v>
+        <v>5.86</v>
       </c>
       <c r="N29" t="n">
-        <v>9.81</v>
+        <v>2.16</v>
       </c>
       <c r="O29" t="n">
-        <v>1.73</v>
+        <v>6</v>
       </c>
       <c r="P29" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>1.91</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
         <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X29" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['8', '31', '57']</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '17', '34', '76', '87']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.65</v>
+        <v>1.1</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.22</v>
+        <v>3.4</v>
       </c>
       <c r="AJ29" t="n">
-        <v>4.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45630.6875</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,16 +4255,16 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -4281,22 +4281,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="M30" t="n">
-        <v>6.34</v>
+        <v>13.3</v>
       </c>
       <c r="N30" t="n">
-        <v>6.89</v>
+        <v>9.81</v>
       </c>
       <c r="O30" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R30" t="n">
         <v>1.29</v>
@@ -4317,29 +4317,29 @@
         <v>1.17</v>
       </c>
       <c r="X30" t="n">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD30" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['34', '36', '50', '75']</t>
+          <t>['8', '31', '57']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45630.6875</v>
@@ -4384,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.91</v>
+        <v>1.18</v>
       </c>
       <c r="M31" t="n">
-        <v>7.88</v>
+        <v>7.22</v>
       </c>
       <c r="N31" t="n">
-        <v>2.17</v>
+        <v>7.85</v>
       </c>
       <c r="O31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q31" t="n">
         <v>4</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.4</v>
-      </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['10', '33', '49', '72']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['35', '62', '90']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['50', '68', '83']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45630.6875</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M32" t="n">
-        <v>5.86</v>
+        <v>7.88</v>
       </c>
       <c r="N32" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U32" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="Z32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.3</v>
       </c>
-      <c r="AA32" t="n">
-        <v>2</v>
-      </c>
       <c r="AB32" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['11']</t>
+          <t>['35', '62', '90']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['7', '17', '34', '76', '87']</t>
+          <t>['50', '68', '83']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>2.9</v>
+        <v>1.99</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45630.6875</v>
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Flint Town United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Aberystwyth Town</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>10.8</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="N33" t="n">
-        <v>1.22</v>
+        <v>5.05</v>
       </c>
       <c r="O33" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.66</v>
+        <v>4.33</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
         <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="U33" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X33" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['3', '25', '50']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z33" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>4.05</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>1.23</v>
+        <v>2.63</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45630.69791666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,16 +4771,16 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Flint Town United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aberystwyth Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -4797,65 +4797,65 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="M34" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="N34" t="n">
-        <v>5.05</v>
+        <v>5.21</v>
       </c>
       <c r="O34" t="n">
         <v>2.2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="U34" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X34" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['3', '25', '50']</t>
+          <t>['26', '35']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45630.69791666666</v>
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3.95</v>
+        <v>4.83</v>
       </c>
       <c r="N35" t="n">
-        <v>5.21</v>
+        <v>5.96</v>
       </c>
       <c r="O35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD35" t="n">
         <v>2.2</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['26', '35']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG35" t="n">
         <v>1.15</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45630.69791666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
         <v>2</v>
       </c>
-      <c r="I36" t="n">
-        <v>1</v>
-      </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.47</v>
+        <v>3.07</v>
       </c>
       <c r="M36" t="n">
-        <v>3.58</v>
+        <v>3.33</v>
       </c>
       <c r="N36" t="n">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
         <v>1.36</v>
@@ -5079,13 +5079,13 @@
         <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U36" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V36" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
         <v>1.25</v>
@@ -5106,32 +5106,32 @@
         <v>1.38</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['34', '42']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['52', '57']</t>
+          <t>['13', '39', '45+3', '68']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45630.69791666666</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,48 +5158,48 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="n">
         <v>2</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="O37" t="n">
         <v>4</v>
       </c>
-      <c r="I37" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" t="n">
-        <v>3</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="M37" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3.5</v>
-      </c>
       <c r="P37" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="R37" t="n">
         <v>1.36</v>
@@ -5208,13 +5208,13 @@
         <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U37" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
         <v>1.25</v>
@@ -5235,32 +5235,32 @@
         <v>1.38</v>
       </c>
       <c r="AC37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>['4']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>['52', '57']</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>['34', '42']</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['13', '39', '45+3', '68']</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.9</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45630.69791666666</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,23 +5287,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>1</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.45</v>
+        <v>10.8</v>
       </c>
       <c r="M38" t="n">
-        <v>4.83</v>
+        <v>5.9</v>
       </c>
       <c r="N38" t="n">
-        <v>5.96</v>
+        <v>1.22</v>
       </c>
       <c r="O38" t="n">
-        <v>2.05</v>
+        <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>1.66</v>
       </c>
       <c r="R38" t="n">
         <v>1.25</v>
       </c>
       <c r="S38" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T38" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X38" t="n">
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
       <c r="AG38" t="n">
-        <v>1.15</v>
+        <v>2.8</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.5</v>
+        <v>1.05</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.36</v>
+        <v>4.05</v>
       </c>
       <c r="AJ38" t="n">
-        <v>3.1</v>
+        <v>1.23</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45630.69791666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="M39" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S39" t="n">
         <v>3.25</v>
       </c>
-      <c r="N39" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T39" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="U39" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="V39" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.33</v>
       </c>
-      <c r="X39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z39" t="n">
+      <c r="AC39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['14', '60', '63', '67']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.75</v>
       </c>
-      <c r="AA39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['54', '71']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AI39" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45630.69791666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.03</v>
+        <v>2.24</v>
       </c>
       <c r="M41" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="N41" t="n">
-        <v>3.64</v>
+        <v>3.16</v>
       </c>
       <c r="O41" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W41" t="n">
         <v>1.33</v>
       </c>
-      <c r="S41" t="n">
+      <c r="X41" t="n">
         <v>3.25</v>
       </c>
-      <c r="T41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.68</v>
-      </c>
       <c r="Y41" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="Z41" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.77</v>
+        <v>3.6</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['14', '60', '63', '67']</t>
+          <t>['54', '71']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45630.69791666666</v>
@@ -6577,19 +6577,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -6603,83 +6603,83 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N48" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="O48" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P48" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z48" t="n">
         <v>2</v>
       </c>
-      <c r="Q48" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z48" t="n">
+      <c r="AA48" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['45', '71', '85']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH48" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45630.83333333334</v>
@@ -6706,25 +6706,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
         <v>3.7</v>
       </c>
       <c r="N49" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="O49" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="P49" t="n">
         <v>2.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T49" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W49" t="n">
         <v>1.36</v>
       </c>
-      <c r="V49" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.3</v>
-      </c>
       <c r="X49" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Y49" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC49" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AD49" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['45', '71', '85']</t>
+          <t>['52', '62']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.65</v>
+        <v>1.15</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45630.83333333334</v>
@@ -6835,109 +6835,109 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P50" t="n">
         <v>2</v>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N50" t="n">
-        <v>4</v>
-      </c>
-      <c r="O50" t="n">
+      <c r="Q50" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S50" t="n">
         <v>2.5</v>
       </c>
-      <c r="P50" t="n">
+      <c r="T50" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y50" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Z50" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA50" t="n">
         <v>4.5</v>
       </c>
-      <c r="R50" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X50" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y50" t="n">
+      <c r="AB50" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC50" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z50" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC50" t="n">
+      <c r="AD50" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD50" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>['52', '62']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45630.83333333334</v>
@@ -7093,22 +7093,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -7119,16 +7119,16 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N52" t="n">
         <v>2.55</v>
       </c>
       <c r="O52" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P52" t="n">
         <v>2.1</v>
@@ -7137,62 +7137,62 @@
         <v>3.2</v>
       </c>
       <c r="R52" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S52" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="T52" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U52" t="n">
         <v>1.33</v>
       </c>
       <c r="V52" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W52" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X52" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Y52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD52" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z52" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>2</v>
-      </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '79', '85']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AJ52" t="n">
         <v>1.83</v>
@@ -7222,25 +7222,25 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
         <v>1</v>
       </c>
-      <c r="H53" t="n">
-        <v>2</v>
-      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -7248,83 +7248,83 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="O53" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="P53" t="n">
         <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R53" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T53" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U53" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W53" t="n">
         <v>1.36</v>
       </c>
-      <c r="V53" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W53" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X53" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Y53" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI53" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z53" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>['61', '90']</t>
-        </is>
-      </c>
-      <c r="AG53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AJ53" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45630.89583333334</v>
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,34 +7377,34 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="M54" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="O54" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="P54" t="n">
         <v>2.1</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R54" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S54" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T54" t="n">
         <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V54" t="n">
         <v>1.06</v>
@@ -7416,44 +7416,44 @@
         <v>3.25</v>
       </c>
       <c r="Y54" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA54" t="n">
         <v>3.5</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AD54" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>['21', '79', '85']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['61', '90']</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI54" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45630.89583333334</v>
